--- a/output/graficos_regionales/plot_regional_serie_i_peringrmin_s_2023_aysen.xlsx
+++ b/output/graficos_regionales/plot_regional_serie_i_peringrmin_s_2023_aysen.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 16:46</t>
+    <t xml:space="preserve">2026-10-05 02:27</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
